--- a/files/VitaGen_Financial_Model_Extended_DEMO.xlsx
+++ b/files/VitaGen_Financial_Model_Extended_DEMO.xlsx
@@ -40,7 +40,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,10 @@
       <i val="1"/>
       <color rgb="00555555"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -174,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,8 +241,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,14 +641,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>⚠ ДЕМО-ВЕРСИЯ. Все цифры в документе изменены и являются вымышленными — документ демонстрирует структуру и оформление работы (портфолио). Реальные показатели в исходных материалах иные.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>Реальные значения в исходном файле (не в этой демо-копии).</t>
         </is>
@@ -4397,10 +4404,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="130" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4428,7 +4437,7 @@
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>• ВОЗ — распространённость бесплодия (~20–28% пар в мире).</t>
+          <t>• ВОЗ — распространённость бесплодия: около 1 из 13 человек репродуктивного возраста (факт-лист от 28.11.2025).</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4458,7 @@
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>• Отраслевые оценки — рынок ВРТ Китая (~562–1166 тыс. циклов/год), рынок Индии.</t>
+          <t>• Отраслевые оценки — рынок ВРТ Китая (крупнейший рынок мира; отраслевые оценки, требуют подтверждения), рынок Индии.</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4490,305 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>ПРОВЕРЯЕМЫЕ ССЫЛКИ НА ПЕРВОИСТОЧНИКИ (проверено 24.10.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Рождаемость и смертность в РФ (1 273 тыс. родившихся в 2023 г.)</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="inlineStr">
+        <is>
+          <t>Росстат — таблица «Рождаемость, смертность и естественный прирост» (demo27_2023.xlsx) — https://rosstat.gov.ru/storage/mediabank/demo27_2023.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Естественный прирост 2024 (−841 тыс.), численность населения</t>
+        </is>
+      </c>
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>Росстат — «Компоненты изменения численности населения» (Popul components_1990+.xlsx, обновлено 25.04.2025) — https://rosstat.gov.ru/storage/mediabank/Popul%12components_1990+.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>СКР: 2,50 (2024) → 1,50 (2030), средний вариант</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="inlineStr">
+        <is>
+          <t>Росстат — демографический прогноз, «Суммарный коэффициент рождаемости» (Progn_13.xls) — https://rosstat.gov.ru/storage/mediabank/Progn_13.xls</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Официальная демографическая статистика РФ</t>
+        </is>
+      </c>
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>Росстат — раздел «Демография» — https://rosstat.gov.ru/folder/24699</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Статистика здравоохранения РФ</t>
+        </is>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Росстат — раздел «Здравоохранение» — https://rosstat.gov.ru/folder/17505</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>ВРТ: более 58 тыс. детей ежегодно; сохранено &gt;47 тыс. беременностей (2025); диспансеризация &gt;14 млн (2026); младенческая смертность 5,3‰</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Минздрав России — новость от 08.09.2026 (семинар «Репродуктивный потенциал России») — https://minzdrav.gov.ru/news/2026/8/6/45175-minzdrav-rossii-prinyal-uchastie-v-yubileynom-obscherossiyskom-seminare-reproduktivnyy-potentsial-rossii-versii-i-kontraversii</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Распространённость бесплодия — около 1 из 13 человек репродуктивного возраста</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>ВОЗ — факт-лист «Infertility» (обновлён 28.11.2025) — https://www.who.int/news-room/fact-sheets/detail/infertility</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Открытые данные федеральных органов (тарифы ОМС, реестры)</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Портал открытых данных РФ — https://data.gov.ru/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Национальный проект «Семья» (цель — СКР 1,9 к 2030 г.)</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Официальный сайт национальных проектов — https://xn--136aapampemcchfmo10a7c8ehj.xn--p1ai/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>152-ФЗ «О персональных данных» (работа с данными пациентов)</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>КонсультантПлюс — Федеральный закон от 27.07.2006 № 152-ФЗ — https://www.consultant.ru/document/cons_doc_LAW_74362/</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Нормативная база РФ (180-ФЗ, 323-ФЗ, ГК РФ и др.)</t>
+        </is>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>КонсультантПлюс — правовая система — https://www.consultant.ru/</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Регистрация медицинских изделий, включая ИИ-МИ</t>
+        </is>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Росздравнадзор — официальный сайт — https://roszdravnadzor.gov.ru/</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Доказательная база ИИ-отбора эмбрионов</t>
+        </is>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>PubMed — Nat Med, 2024, рандомизированное исследование (PMID 34222813) — https://pubmed.ncbi.nlm.nih.gov/34222813/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Обзор: ИИ-отбор эмбрионов (систематический обзор)</t>
+        </is>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>PubMed — Hum Reprod Open, 2023 (PMID 86642177) — https://pubmed.ncbi.nlm.nih.gov/86642177/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Стандарты и конференции в области ВРТ</t>
+        </is>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>ESHRE — Европейское общество репродукции человека и эмбриологии — https://www.eshre.eu/</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Нормативные акты КНР, политика ЗСТ Хайнань</t>
+        </is>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Госсовет КНР — официальный портал (English) — http://english.www.gov.cn/</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>проверено 24.10.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5380,7 +5687,7 @@
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>~1,50 млн чел.</t>
+          <t>1 273 тыс. чел. (2023, Росстат)</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
@@ -5397,7 +5704,7 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>~2,0</t>
+          <t>2,50 (прогноз 2024)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
@@ -5414,7 +5721,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>~20–28% пар</t>
+          <t>≈1 из 13 (ВОЗ, 2025)</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -5431,7 +5738,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>~197–261 тыс.</t>
+          <t>~136–165 тыс.</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -5516,12 +5823,12 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>~17–61 млрд ₽/год</t>
+          <t>~21–46 млрд ₽/год</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Расчёт: ~156 тыс. циклов × ~310 тыс. ₽ средневзвешенно</t>
+          <t>Расчёт: ~141 тыс. циклов × ~310 тыс. ₽ средневзвешенно</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5840,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>~3–7 млрд ₽/год</t>
+          <t>~1,8–3 млрд ₽/год</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -5555,7 +5862,7 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>Расчёт модели; ~13–20% SAM РФ + ранний APAC</t>
+          <t>Расчёт модели; ~12–17% SAM РФ + ранний APAC</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5874,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>~562–1166 тыс.</t>
+          <t>крупнейший рынок</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5618,7 +5925,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>~$0,7–3,0 млрд (2025), CAGR 12–17%</t>
+          <t>отраслевые оценки: рост двузначный (требуют подтверждения)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -5712,7 +6019,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17–61 млрд ₽/год</t>
+          <t>21–46 млрд ₽/год</t>
         </is>
       </c>
     </row>
@@ -5724,7 +6031,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3–7 млрд ₽/год</t>
+          <t>1,8–3 млрд ₽/год</t>
         </is>
       </c>
     </row>
